--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_7.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_7.xlsx
@@ -658,7 +658,7 @@
         <v>0.00846748557122654</v>
       </c>
       <c r="C2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>31738614</v>
+        <v>4144769</v>
       </c>
       <c r="L2" t="n">
-        <v>17940794</v>
+        <v>2092327</v>
       </c>
       <c r="M2" t="n">
-        <v>4201086</v>
+        <v>453534</v>
       </c>
       <c r="N2" t="n">
-        <v>143421</v>
+        <v>13298</v>
       </c>
       <c r="O2" t="n">
-        <v>2460081</v>
+        <v>279275</v>
       </c>
       <c r="P2" t="n">
-        <v>945745</v>
+        <v>111463</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999950528144836</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8823140263557434</v>
+        <v>0.8044283986091614</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7651383876800537</v>
+        <v>0.6264577507972717</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7025456428527832</v>
+        <v>0.530832827091217</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2087851613759995</v>
+        <v>0.1378173977136612</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7476993203163147</v>
+        <v>0.5944386124610901</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8517224788665771</v>
+        <v>0.712046205997467</v>
       </c>
       <c r="X2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>44424660</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="AG2" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AH2" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AI2" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AK2" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564294219017029</v>
+        <v>0.9558094143867493</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113486409187317</v>
+        <v>0.9115616083145142</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8579833507537842</v>
+        <v>0.8578552603721619</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6620163917541504</v>
+        <v>0.6612218618392944</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019670486450195</v>
+        <v>0.9019814133644104</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.931441068649292</v>
+        <v>0.9314774870872498</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029527753233312</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>31738614</v>
+        <v>4144769</v>
       </c>
       <c r="E3" t="n">
-        <v>3587791</v>
+        <v>862233</v>
       </c>
       <c r="F3" t="n">
-        <v>64390</v>
+        <v>26129</v>
       </c>
       <c r="G3" t="n">
-        <v>5649</v>
+        <v>1964</v>
       </c>
       <c r="H3" t="n">
-        <v>3980</v>
+        <v>1865</v>
       </c>
       <c r="I3" t="n">
-        <v>170</v>
+        <v>96</v>
       </c>
       <c r="J3" t="n">
-        <v>70487119</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>75277991</v>
+        <v>10371271</v>
       </c>
       <c r="L3" t="n">
-        <v>86408384</v>
+        <v>11866515</v>
       </c>
       <c r="M3" t="n">
-        <v>106589743</v>
+        <v>15078073</v>
       </c>
       <c r="N3" t="n">
-        <v>113742771</v>
+        <v>16243173</v>
       </c>
       <c r="O3" t="n">
-        <v>110514571</v>
+        <v>15715000</v>
       </c>
       <c r="P3" t="n">
-        <v>113393822</v>
+        <v>16177417</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8965556025505066</v>
+        <v>0.8228551149368286</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7801486849784851</v>
+        <v>0.6336776614189148</v>
       </c>
       <c r="T3" t="n">
-        <v>0.642020583152771</v>
+        <v>0.4839869439601898</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2292099148035049</v>
+        <v>0.1483572274446487</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6896181702613831</v>
+        <v>0.5471024513244629</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6987237930297852</v>
+        <v>0.5760153532028198</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>33898745</v>
+        <v>4822613</v>
       </c>
       <c r="Z3" t="n">
-        <v>1393396</v>
+        <v>198886</v>
       </c>
       <c r="AA3" t="n">
-        <v>60111</v>
+        <v>8613</v>
       </c>
       <c r="AB3" t="n">
-        <v>47831</v>
+        <v>6871</v>
       </c>
       <c r="AC3" t="n">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>70487340</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>77967120</v>
+        <v>11155975</v>
       </c>
       <c r="AG3" t="n">
-        <v>89879810</v>
+        <v>12822698</v>
       </c>
       <c r="AH3" t="n">
-        <v>107439825</v>
+        <v>15345889</v>
       </c>
       <c r="AI3" t="n">
-        <v>114074974</v>
+        <v>16296043</v>
       </c>
       <c r="AJ3" t="n">
-        <v>110995151</v>
+        <v>15855549</v>
       </c>
       <c r="AK3" t="n">
-        <v>113465688</v>
+        <v>16209238</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575752019882202</v>
+        <v>0.9574265480041504</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099511504173279</v>
+        <v>0.9097204804420471</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573793172836304</v>
+        <v>0.8567676544189453</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6614662408828735</v>
+        <v>0.660255491733551</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015187621116638</v>
+        <v>0.9011561870574951</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312731623649597</v>
+        <v>0.9311549663543701</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03201304320695698</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3971440</v>
+        <v>942458</v>
       </c>
       <c r="E4" t="n">
-        <v>17940794</v>
+        <v>2092327</v>
       </c>
       <c r="F4" t="n">
-        <v>964905</v>
+        <v>224234</v>
       </c>
       <c r="G4" t="n">
-        <v>39169</v>
+        <v>12541</v>
       </c>
       <c r="H4" t="n">
-        <v>73581</v>
+        <v>27393</v>
       </c>
       <c r="I4" t="n">
-        <v>6742</v>
+        <v>2925</v>
       </c>
       <c r="J4" t="n">
-        <v>221</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>4233401</v>
+        <v>1007671</v>
       </c>
       <c r="L4" t="n">
-        <v>5506982</v>
+        <v>1247606</v>
       </c>
       <c r="M4" t="n">
-        <v>1778719</v>
+        <v>400848</v>
       </c>
       <c r="N4" t="n">
-        <v>543510</v>
+        <v>83192</v>
       </c>
       <c r="O4" t="n">
-        <v>830120</v>
+        <v>190538</v>
       </c>
       <c r="P4" t="n">
-        <v>164646</v>
+        <v>45076</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999975562095642</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.889377772808075</v>
+        <v>0.8135373592376709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7725705504417419</v>
+        <v>0.6300470232963562</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6709208488464355</v>
+        <v>0.5063286423683167</v>
       </c>
       <c r="U4" t="n">
-        <v>0.218521311879158</v>
+        <v>0.1428932249546051</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7174851894378662</v>
+        <v>0.5697891116142273</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7676741480827332</v>
+        <v>0.6368477344512939</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1441845</v>
+        <v>208181</v>
       </c>
       <c r="Z4" t="n">
-        <v>20925813</v>
+        <v>3003787</v>
       </c>
       <c r="AA4" t="n">
-        <v>581832</v>
+        <v>83142</v>
       </c>
       <c r="AB4" t="n">
-        <v>38644</v>
+        <v>5553</v>
       </c>
       <c r="AC4" t="n">
-        <v>8024</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1544272</v>
+        <v>222967</v>
       </c>
       <c r="AG4" t="n">
-        <v>2035556</v>
+        <v>291423</v>
       </c>
       <c r="AH4" t="n">
-        <v>928637</v>
+        <v>133032</v>
       </c>
       <c r="AI4" t="n">
-        <v>211307</v>
+        <v>30322</v>
       </c>
       <c r="AJ4" t="n">
-        <v>349540</v>
+        <v>49989</v>
       </c>
       <c r="AK4" t="n">
-        <v>92780</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570019841194153</v>
+        <v>0.9566173553466797</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106493592262268</v>
+        <v>0.9106400609016418</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576812148094177</v>
+        <v>0.8573110699653625</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6617411971092224</v>
+        <v>0.6607382893562317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017428159713745</v>
+        <v>0.9015686511993408</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313570857048035</v>
+        <v>0.9313161373138428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>177033</v>
+        <v>46647</v>
       </c>
       <c r="E5" t="n">
-        <v>1645513</v>
+        <v>314453</v>
       </c>
       <c r="F5" t="n">
-        <v>4201086</v>
+        <v>453534</v>
       </c>
       <c r="G5" t="n">
-        <v>156175</v>
+        <v>27384</v>
       </c>
       <c r="H5" t="n">
-        <v>333798</v>
+        <v>84530</v>
       </c>
       <c r="I5" t="n">
-        <v>29926</v>
+        <v>10530</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3661994</v>
+        <v>892289</v>
       </c>
       <c r="L5" t="n">
-        <v>5055840</v>
+        <v>1209552</v>
       </c>
       <c r="M5" t="n">
-        <v>2342452</v>
+        <v>483545</v>
       </c>
       <c r="N5" t="n">
-        <v>482298</v>
+        <v>76337</v>
       </c>
       <c r="O5" t="n">
-        <v>1107228</v>
+        <v>231187</v>
       </c>
       <c r="P5" t="n">
-        <v>407787</v>
+        <v>82044</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999980926513672</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9312918186187744</v>
+        <v>0.8842616677284241</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9080790281295776</v>
+        <v>0.8503193259239197</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9641363024711609</v>
+        <v>0.9461261630058289</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9910730719566345</v>
+        <v>0.9902821183204651</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9831405878067017</v>
+        <v>0.9743101000785828</v>
       </c>
       <c r="W5" t="n">
-        <v>0.995018482208252</v>
+        <v>0.9922563433647156</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>56517</v>
+        <v>8150</v>
       </c>
       <c r="Z5" t="n">
-        <v>598295</v>
+        <v>86254</v>
       </c>
       <c r="AA5" t="n">
-        <v>5610294</v>
+        <v>802859</v>
       </c>
       <c r="AB5" t="n">
-        <v>69798</v>
+        <v>9996</v>
       </c>
       <c r="AC5" t="n">
-        <v>204203</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>4431</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1501863</v>
+        <v>214445</v>
       </c>
       <c r="AG5" t="n">
-        <v>2070821</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>933244</v>
+        <v>134220</v>
       </c>
       <c r="AI5" t="n">
-        <v>211827</v>
+        <v>30453</v>
       </c>
       <c r="AJ5" t="n">
-        <v>351313</v>
+        <v>50456</v>
       </c>
       <c r="AK5" t="n">
-        <v>93024</v>
+        <v>13322</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734916090965271</v>
+        <v>0.9733545184135437</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642650485038757</v>
+        <v>0.9640889763832092</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837973117828369</v>
+        <v>0.9837200045585632</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963177442550659</v>
+        <v>0.9962978363037109</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939009547233582</v>
+        <v>0.9938812851905823</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998383104801178</v>
+        <v>0.9983810186386108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>80372</v>
+        <v>15724</v>
       </c>
       <c r="E6" t="n">
-        <v>143110</v>
+        <v>22481</v>
       </c>
       <c r="F6" t="n">
-        <v>197162</v>
+        <v>26015</v>
       </c>
       <c r="G6" t="n">
-        <v>143421</v>
+        <v>13298</v>
       </c>
       <c r="H6" t="n">
-        <v>56919</v>
+        <v>10743</v>
       </c>
       <c r="I6" t="n">
-        <v>4700</v>
+        <v>1367</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>45519</v>
+        <v>6580</v>
       </c>
       <c r="Z6" t="n">
-        <v>37622</v>
+        <v>5392</v>
       </c>
       <c r="AA6" t="n">
-        <v>76408</v>
+        <v>11005</v>
       </c>
       <c r="AB6" t="n">
-        <v>413892</v>
+        <v>59182</v>
       </c>
       <c r="AC6" t="n">
-        <v>48911</v>
+        <v>6995</v>
       </c>
       <c r="AD6" t="n">
-        <v>3367</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4354</v>
+        <v>2781</v>
       </c>
       <c r="E7" t="n">
-        <v>122571</v>
+        <v>44754</v>
       </c>
       <c r="F7" t="n">
-        <v>527911</v>
+        <v>115764</v>
       </c>
       <c r="G7" t="n">
-        <v>329276</v>
+        <v>37730</v>
       </c>
       <c r="H7" t="n">
-        <v>2460081</v>
+        <v>279275</v>
       </c>
       <c r="I7" t="n">
-        <v>123108</v>
+        <v>30158</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>195</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>5676</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>207971</v>
+        <v>29939</v>
       </c>
       <c r="AB7" t="n">
-        <v>53175</v>
+        <v>7636</v>
       </c>
       <c r="AC7" t="n">
-        <v>3215996</v>
+        <v>460006</v>
       </c>
       <c r="AD7" t="n">
-        <v>84296</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>7997</v>
+        <v>3685</v>
       </c>
       <c r="F8" t="n">
-        <v>24351</v>
+        <v>8706</v>
       </c>
       <c r="G8" t="n">
-        <v>13241</v>
+        <v>3573</v>
       </c>
       <c r="H8" t="n">
-        <v>361842</v>
+        <v>66007</v>
       </c>
       <c r="I8" t="n">
-        <v>945745</v>
+        <v>111463</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>567</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2315</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>1859</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>88087</v>
+        <v>12614</v>
       </c>
       <c r="AD8" t="n">
-        <v>1260508</v>
+        <v>180185</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
